--- a/4_outputs/final/Table08.xlsx
+++ b/4_outputs/final/Table08.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -425,7 +425,7 @@
     <col width="11" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -456,26 +456,46 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>[l]Neither /</t>
+          <t>Neither / unclear %</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>unclear %</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
+          <t>SDG 4-assigned research</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>470002</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>11.8</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>44.4</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>23.8</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>19.9</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SDG 4-assigned research</t>
+          <t>Non-SDG4 research sample</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -485,84 +505,52 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>11.8</t>
+          <t>50.3</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>44.4</t>
+          <t>4.0</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>43.1</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Non-SDG4 research sample</t>
+          <t>SDG 9-assigned research</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>470002</t>
+          <t>577833</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>61.5</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>4.0</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.9</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
-        <is>
-          <t>43.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>SDG 9-assigned research</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>577833</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>61.5</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>2.9</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
         <is>
           <t>33.1</t>
         </is>

--- a/4_outputs/final/Table08.xlsx
+++ b/4_outputs/final/Table08.xlsx
@@ -417,142 +417,408 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="8" customWidth="1" min="5" max="5"/>
-    <col width="21" customWidth="1" min="6" max="6"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Corpus subset</t>
+          <t>SDG</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>Gap</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>ML-only %</t>
+          <t>Research-side distinctive terms</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Education-only %</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Both %</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Neither / unclear %</t>
+          <t>Policy-side distinctive terms</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SDG 4-assigned research</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>470002</t>
+          <t>0.415</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>11.8</t>
+          <t>alleviation, china, approach, zakat, satellite, household, studies, indonesia, literature, relationship</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>44.4</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>23.8</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>19.9</t>
+          <t>social, cent, national, people, protection, services, population, vulnerable, living, million</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Non-SDG4 research sample</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>470002</t>
+          <t>0.299</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>50.3</t>
+          <t>crop, detection, plant, diseases, images, leaf, precision, techniques, soil, yield</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>4.0</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>2.6</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>43.1</t>
+          <t>population, food, children, prevalence, worst, access, hunger, million, births, ratio</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SDG 9-assigned research</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>577833</t>
+          <t>0.494</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>61.5</t>
+          <t>patients, cancer, cells, images, clinical, detection, disease, potential, genes, predict</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2.5</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>2.9</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>33.1</t>
+          <t>health, services, care, national, population, births, mortality, rate, people, access</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>0.267</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>cognitive, brain, neurons, sleep, agricultural, food, cells, motor, memory, poor</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>education, school, secondary, primary, national, quality, children, percent, access, vocational</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>0.278</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>menstrual, poor, pain, mothers, differences, relationship, patients, fertility, stress, sex</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>gender, violence, equality, national, rights, girls, men, cent, sexual, domestic</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>0.292</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>irrigation, soil, agricultural, crop, salinity, agriculture, sup, potential, sub, yield</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>sanitation, access, drinking, supply, national, wastewater, cent, services, population, clean</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>0.428</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>agricultural, poverty, agriculture, battery, optimization, approach, load, drying, poor, artificial</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>access, electricity, renewable, clean, worst best, population, affordable, index worst, cent, national</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>0.387</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>detection, image, food, recognition, leaf, plant, cnn, convolutional, disease, techniques</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>growth, employment, gdp, worst, labour, best, economic, cent, government, tourism</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>0.314</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>agricultural, agriculture, iot, detection, food, crop, plant, farming, farmers, soil</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>infrastructure, innovation, national, government, public, countries, strategy, access, population, intelligence</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>0.271</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>wealth, income inequality, effects, evidence, studies, que, distribution, literature, mobility, poor</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>people, rights, countries, migration, national, cent, disabilities, persons, discrimination, target</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>0.449</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>detection, image, accident, traffic, object, poor, recognition, spatial, fusion, agricultural</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>housing, city, urban, transport, cities, public, waste, national, plan, green</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>0.296</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>food, agricultural, detection, quality, potential, behavior, samples, organic, design, compounds</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>waste, consumption, national, recycling, production, procurement, management, public, economy, circular</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>0.480</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>soil, agricultural, crop, moisture, drought, sub, rice, stress, agriculture, yield</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>climate, change, emissions, countries, national, action, global, energy, nations, united</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>0.358</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>detection, images, aquaculture, food, bacterial, shrimp, cells, imaging, farming, techniques</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>marine, fish caught, biodiversity, rate, ocean, worst, population, sea, embodied, coastal</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>0.239</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>soil, crop, agricultural, plant, spectral, images, sensing, detection, remote, field</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>biodiversity, forest, worst, national, protected, population, area, freshwater, species, best</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0.329</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>poor, food, covid-, pain, image, detection, social, studies, patients, brain</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>international, nations, peace, rights, united, security, human, law, world, global</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0.177</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>sentiment, tweets, covid-, twitter, social, agricultural, dan, yang, zakat, media</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>countries, oecd, international, nations, united, agenda, report, financing, global, challenges</t>
         </is>
       </c>
     </row>
